--- a/output/pdf_financials_xlsx/RY.xlsx
+++ b/output/pdf_financials_xlsx/RY.xlsx
@@ -768,55 +768,35 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -825,55 +805,35 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>38795</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>40669</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>42576</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>46002</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>47181</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>49693</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>48985</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>51464</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>57344</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>66605</v>
       </c>
     </row>
     <row r="13">
@@ -882,55 +842,35 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -939,55 +879,35 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -996,55 +916,35 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1053,55 +953,35 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1110,55 +990,35 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>38795</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>40669</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>42576</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>46002</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>47181</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>49693</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>48985</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>51464</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>57344</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>66605</v>
       </c>
     </row>
     <row r="18">
@@ -1167,55 +1027,35 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E18" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F18" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I18" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1224,55 +1064,35 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E19" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F19" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I19" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1281,55 +1101,35 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1338,55 +1138,35 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1432,15 +1212,11 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>2894</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>3244</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>3329</v>
@@ -1587,55 +1363,35 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>10405</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>11428</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>12400</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>12860</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>11432</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>16038</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>15794</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>14605</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>16230</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>20362</v>
       </c>
     </row>
     <row r="27">
@@ -1644,55 +1400,35 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1775,15 +1511,11 @@
           <t>EPS (Basic)</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B30" s="3" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>7.56</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>8.390000000000001</v>
@@ -1853,55 +1585,35 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B32" s="3" t="n">
+        <v>1534.660767</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>1511.640212</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1483.253589</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>1469.714286</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>1461.892583</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>1450.090416</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>1428.028933</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>1415.213178</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>1442.666667</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>1447.192608</v>
       </c>
     </row>
     <row r="33">
@@ -1910,55 +1622,35 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C33" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E33" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F33" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G33" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H33" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I33" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J33" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B33" s="3" t="n">
+        <v>13299</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>14672</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>15760</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>15914</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>14389</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>20631</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>20109</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>18183</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>19862</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>25651</v>
       </c>
     </row>
     <row r="34">
@@ -1967,55 +1659,35 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>1546</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>1617</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>1652</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>1934</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>2648</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>2592</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>2652</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>2854</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>2981</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>3079</v>
       </c>
     </row>
     <row r="35">
@@ -2024,55 +1696,35 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>14845</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>16289</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>17412</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>17848</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>17037</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>23223</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>22761</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>21037</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>22843</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>28730</v>
       </c>
     </row>
     <row r="36">
@@ -2081,55 +1733,35 @@
           <t>EBITDA Margin %</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>38.26524036602655</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>40.05261993164327</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>40.89627959413754</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>38.79831311682101</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>36.10987473771222</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>46.73294025315437</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>46.46524446259059</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>40.87711798538785</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>39.83503069196428</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>43.13489978229862</v>
       </c>
     </row>
     <row r="37">
@@ -2138,15 +1770,11 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>21.76103466426047</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>22.11014176663032</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>21.12309644670051</v>
@@ -2260,55 +1888,35 @@
           <t>Money Market Investments</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -6058,55 +5666,35 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -6115,55 +5703,35 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -6172,55 +5740,35 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -6229,55 +5777,35 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -6286,55 +5814,35 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -6343,55 +5851,35 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -6400,55 +5888,35 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -6457,55 +5925,35 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -6514,55 +5962,35 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -6571,55 +5999,35 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -6628,55 +6036,35 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -6685,55 +6073,35 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -6742,55 +6110,35 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B127" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C127" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D127" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E127" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F127" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G127" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H127" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I127" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J127" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K127" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -6799,55 +6147,35 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -6856,55 +6184,35 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -6913,55 +6221,35 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -6970,55 +6258,35 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -7027,55 +6295,35 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -7084,55 +6332,35 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -7178,55 +6406,35 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -7235,55 +6443,35 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B136" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C136" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D136" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E136" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F136" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G136" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H136" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I136" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J136" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K136" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -7292,55 +6480,35 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B137" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C137" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D137" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E137" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F137" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G137" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H137" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I137" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J137" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K137" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -7349,55 +6517,35 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B138" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C138" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D138" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E138" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F138" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G138" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H138" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I138" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J138" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K138" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -7406,55 +6554,35 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B139" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C139" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D139" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E139" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F139" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G139" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H139" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I139" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J139" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K139" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -7463,55 +6591,35 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B140" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C140" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D140" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E140" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F140" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G140" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H140" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I140" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J140" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K140" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -7532,35 +6640,23 @@
       <c r="E141" s="3" t="n">
         <v>-6025</v>
       </c>
-      <c r="F141" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G141" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H141" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I141" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J141" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K141" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F141" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -7626,55 +6722,35 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B143" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C143" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D143" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E143" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F143" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G143" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H143" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I143" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J143" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K143" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -7868,55 +6944,35 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B149" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C149" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D149" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E149" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F149" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G149" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H149" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I149" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J149" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K149" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -7925,55 +6981,35 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K150" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B150" s="3" t="n">
+        <v>26856</v>
+      </c>
+      <c r="C150" s="3" t="n">
+        <v>37725</v>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>17474</v>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>14265</v>
+      </c>
+      <c r="F150" s="3" t="n">
+        <v>138819</v>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v>61044</v>
+      </c>
+      <c r="H150" s="3" t="n">
+        <v>21942</v>
+      </c>
+      <c r="I150" s="3" t="n">
+        <v>26079</v>
+      </c>
+      <c r="J150" s="3" t="n">
+        <v>23139</v>
+      </c>
+      <c r="K150" s="3" t="n">
+        <v>55220</v>
       </c>
     </row>
   </sheetData>
@@ -23191,7 +22227,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>Net income attributable to total</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>

--- a/output/pdf_financials_xlsx/RY.xlsx
+++ b/output/pdf_financials_xlsx/RY.xlsx
@@ -431,6 +431,19 @@
   </sheetPr>
   <dimension ref="A1:K150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
